--- a/docs/仕様書/民宿管理システム_フロントエンド設計書.xlsx
+++ b/docs/仕様書/民宿管理システム_フロントエンド設計書.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙" sheetId="1" r:id="Ra87d4246946c47ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更履歴" sheetId="2" r:id="R0a788c52e99c4620"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="3" r:id="R700b3a33a6c9450b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業務要件" sheetId="4" r:id="R200951a860f14b76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="機能一覧" sheetId="5" r:id="R7cf965a3876a4ad5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード行別処理仕様" sheetId="6" r:id="R97ac655c9ee24ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面一覧" sheetId="7" r:id="Rc5a8d15a26e24467"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB設計" sheetId="8" r:id="R7865d4eb5a5f4d0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API一覧" sheetId="9" r:id="R3fb67c9b2c4d4b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非機能要件" sheetId="10" r:id="R6aef9b1521fe4514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト仕様" sheetId="11" r:id="Rfe204ba211354230"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スケジュール" sheetId="12" r:id="R991a9b06bff44fb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考資料" sheetId="13" r:id="Rdb4899852e1b4980"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品質・配備仕様" sheetId="14" r:id="R54ee63fe26e14092"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙" sheetId="1" r:id="R74e42ab3eee344af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更履歴" sheetId="2" r:id="Ra8c71b03a7814f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="3" r:id="R76bf668baf424201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業務要件" sheetId="4" r:id="R5d0e773b2bf8426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="機能一覧" sheetId="5" r:id="R5e6f56e55aa54d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード行別処理仕様" sheetId="6" r:id="R01e0ee3214474e45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面一覧" sheetId="7" r:id="R3bcd0afd29ab4243"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB設計" sheetId="8" r:id="Rd1c7b77d705a484d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API一覧" sheetId="9" r:id="Rced039aaa2c8419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非機能要件" sheetId="10" r:id="Rfd80f5dcd2134038"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト仕様" sheetId="11" r:id="Rb5cf7db0afbc4adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スケジュール" sheetId="12" r:id="R75ba0e89c48f42fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考資料" sheetId="13" r:id="R391f079f5aa046de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品質・配備仕様" sheetId="14" r:id="R87b584eebd8249d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="40">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -272,6 +272,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -603,7 +606,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -615,7 +618,7 @@
         <x:v>備考</x:v>
       </x:c>
       <x:c r="B4" s="22" t="str">
-        <x:v>React フロントエンド実装を基準に更新</x:v>
+        <x:v>React 管理画面と管理端房態カレンダー v1.11 実装を基準に更新</x:v>
       </x:c>
       <x:c r="C4" s="28" t="str">
         <x:v>対象シート</x:v>
@@ -713,7 +716,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B12" s="25" t="str">
-        <x:v>1.9</x:v>
+        <x:v>1.11</x:v>
       </x:c>
       <x:c r="C12" s="25"/>
       <x:c r="D12" s="24" t="str">
@@ -728,7 +731,7 @@
         <x:v>詳細設計</x:v>
       </x:c>
       <x:c r="B13" s="25" t="str">
-        <x:v>コード行別処理仕様</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C13" s="25"/>
       <x:c r="D13" s="24" t="str">
@@ -743,7 +746,7 @@
         <x:v>更新日</x:v>
       </x:c>
       <x:c r="B14" s="25" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="C14" s="25"/>
       <x:c r="D14" s="24" t="str">
@@ -995,7 +998,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -1277,6 +1280,74 @@
       </x:c>
       <x:c r="E20" s="27" t="str">
         <x:v>中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="A21" s="40" t="str">
+        <x:v>FNF-CAL-001</x:v>
+      </x:c>
+      <x:c r="B21" s="40" t="str">
+        <x:v>表示</x:v>
+      </x:c>
+      <x:c r="C21" s="40" t="str">
+        <x:v>自然月全体</x:v>
+      </x:c>
+      <x:c r="D21" s="40" t="str">
+        <x:v>月の日数に応じた横スクロールと固定客室列・日付見出しを提供する。</x:v>
+      </x:c>
+      <x:c r="E21" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" s="40" t="str">
+        <x:v>FNF-CAL-002</x:v>
+      </x:c>
+      <x:c r="B22" s="40" t="str">
+        <x:v>更新</x:v>
+      </x:c>
+      <x:c r="C22" s="40" t="str">
+        <x:v>競合応答保護</x:v>
+      </x:c>
+      <x:c r="D22" s="40" t="str">
+        <x:v>request sequenceにより遅れて到着した旧月応答を画面へ反映しない。</x:v>
+      </x:c>
+      <x:c r="E22" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" s="40" t="str">
+        <x:v>FNF-CAL-003</x:v>
+      </x:c>
+      <x:c r="B23" s="40" t="str">
+        <x:v>操作</x:v>
+      </x:c>
+      <x:c r="C23" s="40" t="str">
+        <x:v>半開区間</x:v>
+      </x:c>
+      <x:c r="D23" s="40" t="str">
+        <x:v>二回目のクリックをendDateExclusiveとして扱い、同日終了・開始を許可する。</x:v>
+      </x:c>
+      <x:c r="E23" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="A24" s="40" t="str">
+        <x:v>FNF-CAL-004</x:v>
+      </x:c>
+      <x:c r="B24" s="40" t="str">
+        <x:v>レスポンシブ</x:v>
+      </x:c>
+      <x:c r="C24" s="40" t="str">
+        <x:v>小画面</x:v>
+      </x:c>
+      <x:c r="D24" s="40" t="str">
+        <x:v>横スクロールを維持し、帯・セル・モーダルの操作可能寸法を保つ。</x:v>
+      </x:c>
+      <x:c r="E24" s="40" t="str">
+        <x:v>高</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1339,7 +1410,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -1660,7 +1731,7 @@
         <x:v>実施済</x:v>
       </x:c>
       <x:c r="H16" s="25" t="str">
-        <x:v>後端テスト共通 logger と連動</x:v>
+        <x:v>後端 mvn verify 123件成功と連動</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -2103,6 +2174,214 @@
       </x:c>
       <x:c r="H33" s="27" t="str">
         <x:v>DOM自動化は未実装</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>FUT-028</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Reservations</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>宿泊数自動表示</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>有効なチェックイン・アウト日</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>日付を変更</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>日付差と同じ N泊/N晚を表示</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>実装確認済</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>読取専用 output / aria-live</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" t="str">
+        <x:v>FUT-029</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Reservations</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>空室候補取得</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>日程・人数入力済</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>入力を変更</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>FAPI-010A を呼び候補だけ表示</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>API自動テスト済</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>条件外 roomId は解除</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>FUT-030</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Reservations</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>入力順序</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>予約フォーム表示</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>日程を選択後に部屋を選択</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>日程未確定時は部屋 select 無効</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>実装確認済</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>取得中・候補なし文言あり</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="36" customHeight="1">
+      <x:c r="A37" s="40" t="str">
+        <x:v>FUT-CAL-001</x:v>
+      </x:c>
+      <x:c r="B37" s="40" t="str">
+        <x:v>date model</x:v>
+      </x:c>
+      <x:c r="C37" s="40" t="str">
+        <x:v>自然月・閏年</x:v>
+      </x:c>
+      <x:c r="D37" s="40" t="str">
+        <x:v>Vitest</x:v>
+      </x:c>
+      <x:c r="E37" s="40" t="str">
+        <x:v>月日配列を生成</x:v>
+      </x:c>
+      <x:c r="F37" s="40" t="str">
+        <x:v>28/29/30/31日を正しく生成</x:v>
+      </x:c>
+      <x:c r="G37" s="40" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="H37" s="40" t="str">
+        <x:v>roomCalendarModel.test.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="36" customHeight="1">
+      <x:c r="A38" s="40" t="str">
+        <x:v>FUT-CAL-002</x:v>
+      </x:c>
+      <x:c r="B38" s="40" t="str">
+        <x:v>date model</x:v>
+      </x:c>
+      <x:c r="C38" s="40" t="str">
+        <x:v>半開区間</x:v>
+      </x:c>
+      <x:c r="D38" s="40" t="str">
+        <x:v>開始日と終了日あり</x:v>
+      </x:c>
+      <x:c r="E38" s="40" t="str">
+        <x:v>normalizedRangeを実行</x:v>
+      </x:c>
+      <x:c r="F38" s="40" t="str">
+        <x:v>二回目の日付をendDateExclusiveとして返す</x:v>
+      </x:c>
+      <x:c r="G38" s="40" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="H38" s="40" t="str">
+        <x:v>同日・逆順はnull</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="36" customHeight="1">
+      <x:c r="A39" s="40" t="str">
+        <x:v>FUT-CAL-003</x:v>
+      </x:c>
+      <x:c r="B39" s="40" t="str">
+        <x:v>calendar band</x:v>
+      </x:c>
+      <x:c r="C39" s="40" t="str">
+        <x:v>月跨ぎ</x:v>
+      </x:c>
+      <x:c r="D39" s="40" t="str">
+        <x:v>前月／翌月へ跨る帯</x:v>
+      </x:c>
+      <x:c r="E39" s="40" t="str">
+        <x:v>bandPlacementを実行</x:v>
+      </x:c>
+      <x:c r="F39" s="40" t="str">
+        <x:v>自然月範囲へ正しくclip</x:v>
+      </x:c>
+      <x:c r="G39" s="40" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="H39" s="40" t="str">
+        <x:v>Vitest</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="36" customHeight="1">
+      <x:c r="A40" s="40" t="str">
+        <x:v>FUT-CAL-004</x:v>
+      </x:c>
+      <x:c r="B40" s="40" t="str">
+        <x:v>conflict</x:v>
+      </x:c>
+      <x:c r="C40" s="40" t="str">
+        <x:v>同日入替</x:v>
+      </x:c>
+      <x:c r="D40" s="40" t="str">
+        <x:v>既存帯あり</x:v>
+      </x:c>
+      <x:c r="E40" s="40" t="str">
+        <x:v>境界日と重複日を比較</x:v>
+      </x:c>
+      <x:c r="F40" s="40" t="str">
+        <x:v>終了日=開始日は非競合、期間交差は競合</x:v>
+      </x:c>
+      <x:c r="G40" s="40" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="H40" s="40" t="str">
+        <x:v>Vitest</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="36" customHeight="1">
+      <x:c r="A41" s="40" t="str">
+        <x:v>FUT-CAL-005</x:v>
+      </x:c>
+      <x:c r="B41" s="40" t="str">
+        <x:v>RoomCalendar</x:v>
+      </x:c>
+      <x:c r="C41" s="40" t="str">
+        <x:v>画面操作</x:v>
+      </x:c>
+      <x:c r="D41" s="40" t="str">
+        <x:v>管理者ログイン済</x:v>
+      </x:c>
+      <x:c r="E41" s="40" t="str">
+        <x:v>月移動、作成、詳細、解除を操作</x:v>
+      </x:c>
+      <x:c r="F41" s="40" t="str">
+        <x:v>API結果と表示が一致</x:v>
+      </x:c>
+      <x:c r="G41" s="40" t="str">
+        <x:v>手動確認対象</x:v>
+      </x:c>
+      <x:c r="H41" s="40" t="str">
+        <x:v>ブラウザ結合確認</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2162,7 +2441,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -2361,7 +2640,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -2581,6 +2860,48 @@
       </x:c>
       <x:c r="D19" s="27" t="str">
         <x:v>package.json / package-lock.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="36" customHeight="1">
+      <x:c r="A20" s="40" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B20" s="40" t="str">
+        <x:v>RoomCalendar.jsx</x:v>
+      </x:c>
+      <x:c r="C20" s="40" t="str">
+        <x:v>自然月 Tape Chart、期間選択、詳細操作、自動更新。</x:v>
+      </x:c>
+      <x:c r="D20" s="40" t="str">
+        <x:v>src/main/frontend/RoomCalendar.jsx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="A21" s="40" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B21" s="40" t="str">
+        <x:v>roomCalendarModel.js</x:v>
+      </x:c>
+      <x:c r="C21" s="40" t="str">
+        <x:v>半開区間、月生成、帯配置、競合、解除preview。</x:v>
+      </x:c>
+      <x:c r="D21" s="40" t="str">
+        <x:v>src/main/frontend/roomCalendarModel.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" s="40" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B22" s="40" t="str">
+        <x:v>白馬樹海_管理端房態カレンダー仕様書.md</x:v>
+      </x:c>
+      <x:c r="C22" s="40" t="str">
+        <x:v>管理端房態カレンダーの統合仕様。</x:v>
+      </x:c>
+      <x:c r="D22" s="40" t="str">
+        <x:v>docs/仕様書/白馬樹海_管理端房態カレンダー仕様書.md</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2637,7 +2958,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="19" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="19" t="str">
         <x:v>何念童</x:v>
@@ -2891,6 +3212,46 @@
       </x:c>
       <x:c r="F16" s="27" t="str">
         <x:v>app.css</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="40" t="str">
+        <x:v>FEQ-CAL-001</x:v>
+      </x:c>
+      <x:c r="B17" s="40" t="str">
+        <x:v>品質</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="str">
+        <x:v>Vitest</x:v>
+      </x:c>
+      <x:c r="D17" s="40" t="str">
+        <x:v>日付モデル8件をnpm run test:frontendで検証し、npm run checkへ統合する。</x:v>
+      </x:c>
+      <x:c r="E17" s="40" t="str">
+        <x:v>frontend test、lint、buildを実行する。</x:v>
+      </x:c>
+      <x:c r="F17" s="40" t="str">
+        <x:v>package.json / roomCalendarModel.test.js</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="40" t="str">
+        <x:v>FEQ-CAL-002</x:v>
+      </x:c>
+      <x:c r="B18" s="40" t="str">
+        <x:v>配備</x:v>
+      </x:c>
+      <x:c r="C18" s="40" t="str">
+        <x:v>房態カレンダーroute</x:v>
+      </x:c>
+      <x:c r="D18" s="40" t="str">
+        <x:v>/calendarは既存app shellを返し、生成app.jsとapp.cssだけで動作する。</x:v>
+      </x:c>
+      <x:c r="E18" s="40" t="str">
+        <x:v>/jukai-internal/calendarを管理者認証後に確認する。</x:v>
+      </x:c>
+      <x:c r="F18" s="40" t="str">
+        <x:v>DashboardController.java / app.js / app.css</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2944,7 +3305,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -3139,6 +3500,36 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="E16" s="27"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>1.10</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>予約フォームの宿泊数自動表示、日程・人数別の空室候補取得、選択順序、一覧の泊数表示を反映</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>何念童</x:v>
+      </x:c>
+      <x:c r="E17"/>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="40" t="str">
+        <x:v>1.11</x:v>
+      </x:c>
+      <x:c r="B18" s="40" t="str">
+        <x:v>2026-09-30</x:v>
+      </x:c>
+      <x:c r="C18" s="40" t="str">
+        <x:v>管理端房態カレンダー、在庫ブロック、半開区間、競合制御、監査、30秒更新、関連テストを反映</x:v>
+      </x:c>
+      <x:c r="D18" s="40" t="str">
+        <x:v>何念童</x:v>
+      </x:c>
+      <x:c r="E18" s="40"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3189,7 +3580,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -3314,6 +3705,34 @@
       </x:c>
       <x:c r="C15" s="27"/>
       <x:c r="D15" s="27"/>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="40" t="str">
+        <x:v>FE-BASE-013</x:v>
+      </x:c>
+      <x:c r="B16" s="40" t="str">
+        <x:v>画面</x:v>
+      </x:c>
+      <x:c r="C16" s="40" t="str">
+        <x:v>房態カレンダー</x:v>
+      </x:c>
+      <x:c r="D16" s="40" t="str">
+        <x:v>管理者向け自然月 Tape Chart を追加し、予約と在庫ブロックを同じ時間軸に表示する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="40" t="str">
+        <x:v>FE-BASE-014</x:v>
+      </x:c>
+      <x:c r="B17" s="40" t="str">
+        <x:v>日付</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="str">
+        <x:v>半開区間</x:v>
+      </x:c>
+      <x:c r="D17" s="40" t="str">
+        <x:v>二回目のクリックは退房日／販売再開日であり、その日付自体は期間に含めない。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3369,7 +3788,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -3492,7 +3911,7 @@
         <x:v>予約登録フォーム</x:v>
       </x:c>
       <x:c r="D10" s="25" t="str">
-        <x:v>客室、日付、宿泊者、連絡先、同行者、支払状態を入力できる。</x:v>
+        <x:v>チェックイン・チェックアウトを先に選択し、宿泊数を自動表示したうえで、日程・人数に合う客室、宿泊者、連絡先、同行者、支払状態を入力できる。</x:v>
       </x:c>
       <x:c r="E10" s="25" t="str">
         <x:v>高</x:v>
@@ -3719,6 +4138,106 @@
       </x:c>
       <x:c r="F21" s="27" t="str">
         <x:v>App.jsx / app.css / app.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>FR-016</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>予約</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>宿泊数自動計算</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>チェックイン日とチェックアウト日の差を宿泊数として読取専用表示する。</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>nightsBetween / stayNights</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>FR-017</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>予約</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>空室候補絞り込み</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>日程と人数の変更時に予約可能客室 API を呼び、条件外になった選択客室は解除する。</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>availableRooms useEffect</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="A24" s="40" t="str">
+        <x:v>FE-CAL-REQ-001</x:v>
+      </x:c>
+      <x:c r="B24" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="C24" s="40" t="str">
+        <x:v>房態確認</x:v>
+      </x:c>
+      <x:c r="D24" s="40" t="str">
+        <x:v>自然月の全客室について予約・販売停止・メンテナンスを一画面で確認できる。</x:v>
+      </x:c>
+      <x:c r="E24" s="40" t="str">
+        <x:v>月移動と30秒更新で最新状態を表示</x:v>
+      </x:c>
+      <x:c r="F24" s="40" t="str">
+        <x:v>FE-CAL-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="36" customHeight="1">
+      <x:c r="A25" s="40" t="str">
+        <x:v>FE-CAL-REQ-002</x:v>
+      </x:c>
+      <x:c r="B25" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="C25" s="40" t="str">
+        <x:v>空き期間操作</x:v>
+      </x:c>
+      <x:c r="D25" s="40" t="str">
+        <x:v>開始日と退房日／再開日を順に選び、直接予約または在庫ブロックを登録できる。</x:v>
+      </x:c>
+      <x:c r="E25" s="40" t="str">
+        <x:v>終了日は半開区間の末尾</x:v>
+      </x:c>
+      <x:c r="F25" s="40" t="str">
+        <x:v>FE-CAL-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="36" customHeight="1">
+      <x:c r="A26" s="40" t="str">
+        <x:v>FE-CAL-REQ-003</x:v>
+      </x:c>
+      <x:c r="B26" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="C26" s="40" t="str">
+        <x:v>詳細操作</x:v>
+      </x:c>
+      <x:c r="D26" s="40" t="str">
+        <x:v>帯を選択し、予約の許可操作またはブロック更新・部分解除を実行できる。</x:v>
+      </x:c>
+      <x:c r="E26" s="40" t="str">
+        <x:v>APIのallowedActionsに従う</x:v>
+      </x:c>
+      <x:c r="F26" s="40" t="str">
+        <x:v>FE-CAL-003</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3784,7 +4303,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -4155,7 +4674,7 @@
         <x:v>予約登録</x:v>
       </x:c>
       <x:c r="D17" s="25" t="str">
-        <x:v>予約本体と同行者配列を POST /api/reservations へ送信する。</x:v>
+        <x:v>日程から宿泊数を自動計算し、人数と合わせて予約可能客室を取得してから予約本体と同行者配列を送信する。</x:v>
       </x:c>
       <x:c r="E17" s="25" t="str">
         <x:v>ReservationCreateRequest</x:v>
@@ -4461,6 +4980,180 @@
       </x:c>
       <x:c r="I27" s="27" t="str">
         <x:v>Notice</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>FE-019</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Reservations</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>宿泊数自動表示</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>日付差をUTC基準で計算し、N泊/N晚を読取専用 output に表示する。</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>checkInDate / checkOutDate</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>stayNights</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>社内</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>nightsBetween / Reservations</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>FE-020</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Reservations</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>予約可能客室取得</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>有効な日程・人数の変更時に API を呼び、候補だけを部屋 select に表示する。</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>dates / guestCount</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>availableRooms</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>社内</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>Reservations.useEffect</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="36" customHeight="1">
+      <x:c r="A30" s="40" t="str">
+        <x:v>FE-CAL-001</x:v>
+      </x:c>
+      <x:c r="B30" s="40" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="C30" s="40" t="str">
+        <x:v>自然月 Tape Chart</x:v>
+      </x:c>
+      <x:c r="D30" s="40" t="str">
+        <x:v>客室行と日付列を固定し、状態別の帯を描画する。</x:v>
+      </x:c>
+      <x:c r="E30" s="40" t="str">
+        <x:v>CalendarView</x:v>
+      </x:c>
+      <x:c r="F30" s="40" t="str">
+        <x:v>月間グリッド</x:v>
+      </x:c>
+      <x:c r="G30" s="40" t="str">
+        <x:v>社内</x:v>
+      </x:c>
+      <x:c r="H30" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I30" s="40" t="str">
+        <x:v>RoomCalendar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="36" customHeight="1">
+      <x:c r="A31" s="40" t="str">
+        <x:v>FE-CAL-002</x:v>
+      </x:c>
+      <x:c r="B31" s="40" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="C31" s="40" t="str">
+        <x:v>期間選択</x:v>
+      </x:c>
+      <x:c r="D31" s="40" t="str">
+        <x:v>空きセルを開始日、退房日／販売再開日の順に選ぶ。</x:v>
+      </x:c>
+      <x:c r="E31" s="40" t="str">
+        <x:v>roomId / [start,end)</x:v>
+      </x:c>
+      <x:c r="F31" s="40" t="str">
+        <x:v>登録モーダル</x:v>
+      </x:c>
+      <x:c r="G31" s="40" t="str">
+        <x:v>社内</x:v>
+      </x:c>
+      <x:c r="H31" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I31" s="40" t="str">
+        <x:v>normalizedRange</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="36" customHeight="1">
+      <x:c r="A32" s="40" t="str">
+        <x:v>FE-CAL-003</x:v>
+      </x:c>
+      <x:c r="B32" s="40" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="C32" s="40" t="str">
+        <x:v>詳細・操作</x:v>
+      </x:c>
+      <x:c r="D32" s="40" t="str">
+        <x:v>予約・ブロック詳細を必要時に取得し、許可操作だけ表示する。</x:v>
+      </x:c>
+      <x:c r="E32" s="40" t="str">
+        <x:v>event</x:v>
+      </x:c>
+      <x:c r="F32" s="40" t="str">
+        <x:v>detail modal</x:v>
+      </x:c>
+      <x:c r="G32" s="40" t="str">
+        <x:v>社内</x:v>
+      </x:c>
+      <x:c r="H32" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I32" s="40" t="str">
+        <x:v>actionAllowed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="36" customHeight="1">
+      <x:c r="A33" s="40" t="str">
+        <x:v>FE-CAL-004</x:v>
+      </x:c>
+      <x:c r="B33" s="40" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="C33" s="40" t="str">
+        <x:v>自動更新</x:v>
+      </x:c>
+      <x:c r="D33" s="40" t="str">
+        <x:v>表示中30秒ごと、タブ復帰時に再取得し、古い応答を破棄する。</x:v>
+      </x:c>
+      <x:c r="E33" s="40" t="str">
+        <x:v>visibility / sequence</x:v>
+      </x:c>
+      <x:c r="F33" s="40" t="str">
+        <x:v>最新CalendarView</x:v>
+      </x:c>
+      <x:c r="G33" s="40" t="str">
+        <x:v>社内</x:v>
+      </x:c>
+      <x:c r="H33" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I33" s="40" t="str">
+        <x:v>RoomCalendar.useEffect</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4512,7 +5205,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -5655,7 +6348,7 @@
         <x:v>処理内容</x:v>
       </x:c>
       <x:c r="B107" s="22" t="str">
-        <x:v>`Reservations` は予約登録、同行者入力、予約一覧、取消一覧、チェックアウト一覧、支払更新、取消、清掃更新を担当する。宿泊人数に応じて同行者配列を生成して API へ送信する。</x:v>
+        <x:v>`Reservations` は日付差による宿泊数表示、日程・人数別の予約可能客室取得、予約登録、同行者入力、3種類の予約一覧、支払・取消・清掃更新を担当する。</x:v>
       </x:c>
       <x:c r="C107" s="27"/>
       <x:c r="D107" s="27"/>
@@ -5743,10 +6436,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B115" s="25" t="str">
-        <x:v>form defaults = guestCount 1 / 公式 / unpaid</x:v>
+        <x:v>form defaults + availableRooms / availabilityState</x:v>
       </x:c>
       <x:c r="C115" s="25" t="str">
-        <x:v>予約登録フォーム初期値を保持する。</x:v>
+        <x:v>フォーム初期値、絞り込み客室、取得中・エラー状態を保持する。</x:v>
       </x:c>
       <x:c r="D115" s="27"/>
     </x:row>
@@ -5755,10 +6448,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B116" s="25" t="str">
-        <x:v>companions = max(0, guestCount - 1)</x:v>
+        <x:v>stayNights = nightsBetween(checkInDate, checkOutDate)</x:v>
       </x:c>
       <x:c r="C116" s="25" t="str">
-        <x:v>代表者以外の同行者入力数を算出する。</x:v>
+        <x:v>UTC基準の日付差を N泊/N晚として読取専用表示する。</x:v>
       </x:c>
       <x:c r="D116" s="27"/>
     </x:row>
@@ -5767,10 +6460,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B117" s="25" t="str">
-        <x:v>submit -&gt; reservation + companion arrays</x:v>
+        <x:v>available-rooms useEffect</x:v>
       </x:c>
       <x:c r="C117" s="25" t="str">
-        <x:v>数値変換、連絡先NULL化、同行者配列をまとめてPOSTする。</x:v>
+        <x:v>有効な日程・人数で候補を取得し、条件外になった roomId を解除する。</x:v>
       </x:c>
       <x:c r="D117" s="27"/>
     </x:row>
@@ -7203,7 +7896,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -7350,6 +8043,29 @@
         <x:v>Nav</x:v>
       </x:c>
       <x:c r="G10" s="25" t="str">
+        <x:v>同画面</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="40" t="str">
+        <x:v>FS-CAL-001</x:v>
+      </x:c>
+      <x:c r="B11" s="40" t="str">
+        <x:v>房態カレンダー</x:v>
+      </x:c>
+      <x:c r="C11" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D11" s="40" t="str">
+        <x:v>自然月 Tape Chart で全客室の予約・販売停止・メンテナンスを管理する。</x:v>
+      </x:c>
+      <x:c r="E11" s="40" t="str">
+        <x:v>月移動、凡例、帯、期間選択、詳細モーダル</x:v>
+      </x:c>
+      <x:c r="F11" s="40" t="str">
+        <x:v>Nav</x:v>
+      </x:c>
+      <x:c r="G11" s="40" t="str">
         <x:v>同画面</x:v>
       </x:c>
     </x:row>
@@ -7410,7 +8126,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -7804,7 +8520,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>何念童</x:v>
@@ -8336,6 +9052,240 @@
         <x:v>CheckoutRow</x:v>
       </x:c>
     </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>FAPI-010A</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>Reservation</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>/api/reservations/available-rooms</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>日程・人数別の予約可能客室取得</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>checkInDate / checkOutDate / guestCount</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>List&lt;Room&gt;</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>Reservations.useEffect</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="36" customHeight="1">
+      <x:c r="A26" s="40" t="str">
+        <x:v>FAPI-CAL-001</x:v>
+      </x:c>
+      <x:c r="B26" s="40" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="C26" s="40" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="D26" s="40" t="str">
+        <x:v>/api/room-calendar?month=YYYY-MM</x:v>
+      </x:c>
+      <x:c r="E26" s="40" t="str">
+        <x:v>月間房態取得</x:v>
+      </x:c>
+      <x:c r="F26" s="40" t="str">
+        <x:v>month</x:v>
+      </x:c>
+      <x:c r="G26" s="40" t="str">
+        <x:v>CalendarView</x:v>
+      </x:c>
+      <x:c r="H26" s="40" t="str">
+        <x:v>RoomCalendar.load</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="36" customHeight="1">
+      <x:c r="A27" s="40" t="str">
+        <x:v>FAPI-CAL-002</x:v>
+      </x:c>
+      <x:c r="B27" s="40" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="C27" s="40" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="D27" s="40" t="str">
+        <x:v>/api/room-calendar/reservations/{id}</x:v>
+      </x:c>
+      <x:c r="E27" s="40" t="str">
+        <x:v>予約詳細取得</x:v>
+      </x:c>
+      <x:c r="F27" s="40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G27" s="40" t="str">
+        <x:v>ReservationDetail</x:v>
+      </x:c>
+      <x:c r="H27" s="40" t="str">
+        <x:v>openStay</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="36" customHeight="1">
+      <x:c r="A28" s="40" t="str">
+        <x:v>FAPI-CAL-003</x:v>
+      </x:c>
+      <x:c r="B28" s="40" t="str">
+        <x:v>Inventory</x:v>
+      </x:c>
+      <x:c r="C28" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D28" s="40" t="str">
+        <x:v>/api/room-calendar/blocks</x:v>
+      </x:c>
+      <x:c r="E28" s="40" t="str">
+        <x:v>ブロック作成</x:v>
+      </x:c>
+      <x:c r="F28" s="40" t="str">
+        <x:v>block payload</x:v>
+      </x:c>
+      <x:c r="G28" s="40" t="str">
+        <x:v>BlockView</x:v>
+      </x:c>
+      <x:c r="H28" s="40" t="str">
+        <x:v>submitRange</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="36" customHeight="1">
+      <x:c r="A29" s="40" t="str">
+        <x:v>FAPI-CAL-004</x:v>
+      </x:c>
+      <x:c r="B29" s="40" t="str">
+        <x:v>Inventory</x:v>
+      </x:c>
+      <x:c r="C29" s="40" t="str">
+        <x:v>PUT</x:v>
+      </x:c>
+      <x:c r="D29" s="40" t="str">
+        <x:v>/api/room-calendar/blocks/{id}</x:v>
+      </x:c>
+      <x:c r="E29" s="40" t="str">
+        <x:v>ブロック更新</x:v>
+      </x:c>
+      <x:c r="F29" s="40" t="str">
+        <x:v>version / period</x:v>
+      </x:c>
+      <x:c r="G29" s="40" t="str">
+        <x:v>BlockView</x:v>
+      </x:c>
+      <x:c r="H29" s="40" t="str">
+        <x:v>saveBlock</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="36" customHeight="1">
+      <x:c r="A30" s="40" t="str">
+        <x:v>FAPI-CAL-005</x:v>
+      </x:c>
+      <x:c r="B30" s="40" t="str">
+        <x:v>Inventory</x:v>
+      </x:c>
+      <x:c r="C30" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D30" s="40" t="str">
+        <x:v>/api/room-calendar/blocks/{id}/release</x:v>
+      </x:c>
+      <x:c r="E30" s="40" t="str">
+        <x:v>全部／一部解除</x:v>
+      </x:c>
+      <x:c r="F30" s="40" t="str">
+        <x:v>release range</x:v>
+      </x:c>
+      <x:c r="G30" s="40" t="str">
+        <x:v>ReleaseResult</x:v>
+      </x:c>
+      <x:c r="H30" s="40" t="str">
+        <x:v>releaseBlock</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="36" customHeight="1">
+      <x:c r="A31" s="40" t="str">
+        <x:v>FAPI-CAL-006</x:v>
+      </x:c>
+      <x:c r="B31" s="40" t="str">
+        <x:v>Booking</x:v>
+      </x:c>
+      <x:c r="C31" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D31" s="40" t="str">
+        <x:v>/api/booking-requests/{id}/cancel</x:v>
+      </x:c>
+      <x:c r="E31" s="40" t="str">
+        <x:v>グループ取消</x:v>
+      </x:c>
+      <x:c r="F31" s="40" t="str">
+        <x:v>reason</x:v>
+      </x:c>
+      <x:c r="G31" s="40" t="str">
+        <x:v>MessageResponse</x:v>
+      </x:c>
+      <x:c r="H31" s="40" t="str">
+        <x:v>runStayAction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="36" customHeight="1">
+      <x:c r="A32" s="40" t="str">
+        <x:v>FAPI-CAL-007</x:v>
+      </x:c>
+      <x:c r="B32" s="40" t="str">
+        <x:v>Room</x:v>
+      </x:c>
+      <x:c r="C32" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D32" s="40" t="str">
+        <x:v>/api/rooms/{id}/cleaning-status</x:v>
+      </x:c>
+      <x:c r="E32" s="40" t="str">
+        <x:v>清掃完了</x:v>
+      </x:c>
+      <x:c r="F32" s="40" t="str">
+        <x:v>cleaningStatus</x:v>
+      </x:c>
+      <x:c r="G32" s="40" t="str">
+        <x:v>MessageResponse</x:v>
+      </x:c>
+      <x:c r="H32" s="40" t="str">
+        <x:v>runStayAction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="36" customHeight="1">
+      <x:c r="A33" s="40" t="str">
+        <x:v>FAPI-CAL-008</x:v>
+      </x:c>
+      <x:c r="B33" s="40" t="str">
+        <x:v>Reservation</x:v>
+      </x:c>
+      <x:c r="C33" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D33" s="40" t="str">
+        <x:v>/api/reservations/{id}/cancel</x:v>
+      </x:c>
+      <x:c r="E33" s="40" t="str">
+        <x:v>直接予約取消</x:v>
+      </x:c>
+      <x:c r="F33" s="40" t="str">
+        <x:v>reason</x:v>
+      </x:c>
+      <x:c r="G33" s="40" t="str">
+        <x:v>MessageResponse</x:v>
+      </x:c>
+      <x:c r="H33" s="40" t="str">
+        <x:v>runStayAction</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
